--- a/data/menu_limpio.xlsx
+++ b/data/menu_limpio.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.99</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
         <v>150</v>
@@ -538,11 +538,11 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/5Y8EYfLHcEeRW1ewsD0R</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/5Y8EYfLHcEeRW1ewsD0R</t>
         </is>
       </c>
       <c r="M2" s="1" t="n">
-        <v>46313.97806712963</v>
+        <v>46323.66144675926</v>
       </c>
     </row>
     <row r="3">
@@ -570,7 +570,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.49</v>
+        <v>30</v>
       </c>
       <c r="G3" t="n">
         <v>180</v>
@@ -595,11 +595,11 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/65X77fVGaX7hHHxba9uK</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/65X77fVGaX7hHHxba9uK</t>
         </is>
       </c>
       <c r="M3" s="1" t="n">
-        <v>46313.97809027778</v>
+        <v>46323.66146990741</v>
       </c>
     </row>
     <row r="4">
@@ -608,7 +608,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBRuqKffWURLLr59BExM</t>
+          <t>Btm3AYbZe22N2u7vedCj</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -618,23 +618,23 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Encurtido Yucateco</t>
+          <t>Guacamole Fresco</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Mezcla de vegetales encurtidos con habanero y vinagre</t>
+          <t>Guacamole preparado al momento con aguacate, limón y cilantro</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.99</v>
+        <v>30</v>
       </c>
       <c r="G4" t="n">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>150g</t>
+          <t>120g</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -642,21 +642,21 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Cebolla, zanahoria, habanero, vinagre, especias</t>
+          <t>Aguacate, limón, cilantro, cebolla, sal</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Encurtido tradicional yucateco picoso y refrescante, acompañamiento perfecto.</t>
+          <t>Guacamole preparado al momento con aguacates frescos y cítricos naturales.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/IBRuqKffWURLLr59BExM</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/Btm3AYbZe22N2u7vedCj</t>
         </is>
       </c>
       <c r="M4" s="1" t="n">
-        <v>46313.97815972222</v>
+        <v>46323.66150462963</v>
       </c>
     </row>
     <row r="5">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.99</v>
+        <v>30</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -709,11 +709,11 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/QjmVjCdAsJAzMpRAp3m4</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/QjmVjCdAsJAzMpRAp3m4</t>
         </is>
       </c>
       <c r="M5" s="1" t="n">
-        <v>46313.97818287037</v>
+        <v>46323.66155092593</v>
       </c>
     </row>
     <row r="6">
@@ -722,7 +722,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Btm3AYbZe22N2u7vedCj</t>
+          <t>IBRuqKffWURLLr59BExM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -732,23 +732,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Guacamole Fresco</t>
+          <t>Encurtido Yucateco</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Guacamole preparado al momento con aguacate, limón y cilantro</t>
+          <t>Mezcla de vegetales encurtidos con habanero y vinagre</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.49</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>120g</t>
+          <t>150g</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -756,21 +756,21 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Aguacate, limón, cilantro, cebolla, sal</t>
+          <t>Cebolla, zanahoria, habanero, vinagre, especias</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Guacamole preparado al momento con aguacates frescos y cítricos naturales.</t>
+          <t>Encurtido tradicional yucateco picoso y refrescante, acompañamiento perfecto.</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/Btm3AYbZe22N2u7vedCj</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/IBRuqKffWURLLr59BExM</t>
         </is>
       </c>
       <c r="M6" s="1" t="n">
-        <v>46313.978125</v>
+        <v>46323.66152777777</v>
       </c>
     </row>
     <row r="7">
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>30</v>
       </c>
       <c r="G7" t="n">
         <v>60</v>
@@ -823,11 +823,11 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/FctNe184ZWZnX2XwYpfl</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/FctNe184ZWZnX2XwYpfl</t>
         </is>
       </c>
       <c r="M7" s="1" t="n">
-        <v>46313.97824074074</v>
+        <v>46323.66158564815</v>
       </c>
     </row>
     <row r="8">
@@ -836,7 +836,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RKdbHvuvIy5mfHXZ5BFQ</t>
+          <t>Fn4o13x0HonmujR7OSlq</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Agua de Horchata</t>
+          <t>Jugo Natural</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bebida dulce de arroz con leche y canela</t>
+          <t>Jugo fresco del día - naranja, piña o sandía</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.99</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -866,25 +866,25 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Arroz, leche, canela, azúcar, agua</t>
+          <t>Frutas frescas de temporada, agua, azúcar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Horchata casera hecha con arroz, leche y canela. Deliciosamente refrescante.</t>
+          <t>Jugo 100% natural hecho del día con frutas frescas de temporada.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/RKdbHvuvIy5mfHXZ5BFQ</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/Fn4o13x0HonmujR7OSlq</t>
         </is>
       </c>
       <c r="M8" s="1" t="n">
-        <v>46313.97829861111</v>
+        <v>46323.6616087963</v>
       </c>
     </row>
     <row r="9">
@@ -893,7 +893,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>wcgzxhvFg8Dpc49o7aoD</t>
+          <t>RKdbHvuvIy5mfHXZ5BFQ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -903,45 +903,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Refresco Mexicano</t>
+          <t>Agua de Horchata</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Refresco embotellado de marca mexicana</t>
+          <t>Bebida dulce de arroz con leche y canela</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.49</v>
+        <v>30</v>
       </c>
       <c r="G9" t="n">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>500ml</t>
+          <t>350ml</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bebida carbonatada, azúcar, saborizantes naturales</t>
+          <t>Arroz, leche, canela, azúcar, agua</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Refresco embotellado frío, sabores mexicanos tradicionales.</t>
+          <t>Horchata casera hecha con arroz, leche y canela. Deliciosamente refrescante.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/wcgzxhvFg8Dpc49o7aoD</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/RKdbHvuvIy5mfHXZ5BFQ</t>
         </is>
       </c>
       <c r="M9" s="1" t="n">
-        <v>46313.9783912037</v>
+        <v>46323.66163194444</v>
       </c>
     </row>
     <row r="10">
@@ -950,7 +950,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fn4o13x0HonmujR7OSlq</t>
+          <t>hgF4rThp91NKAdev48GF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -960,45 +960,45 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jugo Natural</t>
+          <t>Cerveza Corona</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jugo fresco del día - naranja, piña o sandía</t>
+          <t>Cerveza mexicana fría</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.99</v>
+        <v>49</v>
       </c>
       <c r="G10" t="n">
-        <v>110</v>
+        <v>148</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>350ml</t>
+          <t>355ml</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Frutas frescas de temporada, agua, azúcar</t>
+          <t>Malta, lúpulo, levadura, agua</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Jugo 100% natural hecho del día con frutas frescas de temporada.</t>
+          <t>Cerveza mexicana premium, fría y refrescante para disfrutar con tus platillos.</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/Fn4o13x0HonmujR7OSlq</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/hgF4rThp91NKAdev48GF</t>
         </is>
       </c>
       <c r="M10" s="1" t="n">
-        <v>46313.97827546296</v>
+        <v>46323.66166666667</v>
       </c>
     </row>
     <row r="11">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hgF4rThp91NKAdev48GF</t>
+          <t>wcgzxhvFg8Dpc49o7aoD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1017,45 +1017,45 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cerveza Corona</t>
+          <t>Jugo Preparado</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cerveza mexicana fría</t>
+          <t>Bebida refrescante de piña y choconostle</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.49</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>355ml</t>
+          <t>500ml</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Malta, lúpulo, levadura, agua</t>
+          <t>Bebida carbonatada, azúcar, saborizantes naturales</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Cerveza mexicana premium, fría y refrescante para disfrutar con tus platillos.</t>
+          <t>Refresco embotellado frío, sabores mexicanos tradicionales.</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/hgF4rThp91NKAdev48GF</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/wcgzxhvFg8Dpc49o7aoD</t>
         </is>
       </c>
       <c r="M11" s="1" t="n">
-        <v>46313.97833333333</v>
+        <v>46323.66171296296</v>
       </c>
     </row>
     <row r="12">
@@ -1064,55 +1064,55 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>wTzSwwQEZx6NVaWDNgSc</t>
+          <t>jjiW0ffcEur250BXDgiE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Principales</t>
+          <t>Bebidas</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Pibil Quesadilla</t>
+          <t>Taco de asada</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Quesadilla rellena de cochinita pibil y queso Oaxaca</t>
+          <t>Este es una descripcion de pureba</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.99</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>420</v>
+        <v>277</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>220g</t>
+          <t>350 gr</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Tortilla de maíz, cochinita pibil, queso Oaxaca, cebolla</t>
+          <t>Taco de asada</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Quesadilla crujiente con queso Oaxaca derretido y cochinita pibil suculenta.</t>
+          <t>Descricpcion detallada del platillo</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/wTzSwwQEZx6NVaWDNgSc</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/jjiW0ffcEur250BXDgiE</t>
         </is>
       </c>
       <c r="M12" s="1" t="n">
-        <v>46313.97791666666</v>
+        <v>46323.66168981481</v>
       </c>
     </row>
     <row r="13">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XuN5cJ6SjLBPZvCtW8mZ</t>
+          <t>wTzSwwQEZx6NVaWDNgSc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1131,23 +1131,23 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Orden de Tacos (3)</t>
+          <t>Pibil Quesadilla</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tres tacos de cochinita pibil con cebolla morada y cilantro</t>
+          <t>Quesadilla rellena de cochinita pibil y queso Oaxaca</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>6.99</v>
+        <v>35</v>
       </c>
       <c r="G13" t="n">
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3 tacos</t>
+          <t>220g</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1155,21 +1155,21 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Tortillas de maíz, cochinita pibil, cebolla morada, cilantro</t>
+          <t>Tortilla de maíz, cochinita pibil, queso Oaxaca, cebolla</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tacos tradicionales con tortillas hechas a mano, rellenas de cochinita pibil jugosa.</t>
+          <t>Quesadilla crujiente con queso Oaxaca derretido y cochinita pibil suculenta.</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/XuN5cJ6SjLBPZvCtW8mZ</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/wTzSwwQEZx6NVaWDNgSc</t>
         </is>
       </c>
       <c r="M13" s="1" t="n">
-        <v>46313.97782407407</v>
+        <v>46323.66130787037</v>
       </c>
     </row>
     <row r="14">
@@ -1197,7 +1197,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>7.49</v>
+        <v>49</v>
       </c>
       <c r="G14" t="n">
         <v>400</v>
@@ -1222,11 +1222,11 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/5rqbawmWQLQbZalABFDQ</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/5rqbawmWQLQbZalABFDQ</t>
         </is>
       </c>
       <c r="M14" s="1" t="n">
-        <v>46313.9777662037</v>
+        <v>46323.66116898148</v>
       </c>
     </row>
     <row r="15">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KKdcIWT8KfAetqcwUWk3</t>
+          <t>5THL9Bo6TBrD9AuIMWdH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1245,23 +1245,23 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Burrito de Cochinita</t>
+          <t>Pibil Enchiladas (3)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Burrito relleno de cochinita pibil, arroz y frijoles</t>
+          <t>Enchiladas rellenas de cochinita pibil con salsa roja y crema</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>7.99</v>
+        <v>69</v>
       </c>
       <c r="G15" t="n">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>280g</t>
+          <t>3 enchiladas</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1269,21 +1269,21 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Tortilla de harina, cochinita pibil, arroz, frijoles, queso</t>
+          <t>Tortillas, cochinita pibil, salsa roja, crema mexicana, queso</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Burrito abundante relleno de cochinita pibil, arroz blanco y frijoles refritos. Perfecto para llevar.</t>
+          <t>Enchiladas bañadas en salsa roja casera, cubiertas con crema mexicana y queso fresco.</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/KKdcIWT8KfAetqcwUWk3</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/5THL9Bo6TBrD9AuIMWdH</t>
         </is>
       </c>
       <c r="M15" s="1" t="n">
-        <v>46313.97778935185</v>
+        <v>46323.66114583334</v>
       </c>
     </row>
     <row r="16">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5THL9Bo6TBrD9AuIMWdH</t>
+          <t>KKdcIWT8KfAetqcwUWk3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1302,23 +1302,23 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pibil Enchiladas (3)</t>
+          <t>Burrito de Cochinita</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Enchiladas rellenas de cochinita pibil con salsa roja y crema</t>
+          <t>Burrito relleno de cochinita pibil, arroz y frijoles</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>8.49</v>
+        <v>69</v>
       </c>
       <c r="G16" t="n">
-        <v>480</v>
+        <v>520</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3 enchiladas</t>
+          <t>280g</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1326,21 +1326,21 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Tortillas, cochinita pibil, salsa roja, crema mexicana, queso</t>
+          <t>Tortilla de harina, cochinita pibil, arroz, frijoles, queso</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Enchiladas bañadas en salsa roja casera, cubiertas con crema mexicana y queso fresco.</t>
+          <t>Burrito abundante relleno de cochinita pibil, arroz blanco y frijoles refritos. Perfecto para llevar.</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/5THL9Bo6TBrD9AuIMWdH</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/KKdcIWT8KfAetqcwUWk3</t>
         </is>
       </c>
       <c r="M16" s="1" t="n">
-        <v>46313.97773148148</v>
+        <v>46323.6612037037</v>
       </c>
     </row>
     <row r="17">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>b12gUIRdrXZktUcZUoE2</t>
+          <t>XuN5cJ6SjLBPZvCtW8mZ</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1359,45 +1359,45 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cochinita Pibil Tradicional</t>
+          <t>Orden de Tacos (3)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Carne de cerdo marinada en achiote, cocida lentamente en hojas de plátano</t>
+          <t>Tres tacos de cochinita pibil con cebolla morada y cilantro</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.99</v>
+        <v>79</v>
       </c>
       <c r="G17" t="n">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>200g</t>
+          <t>3 tacos</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Cerdo, achiote, cítricos, hojas de plátano, especias yucatecas</t>
+          <t>Tortillas de maíz, cochinita pibil, cebolla morada, cilantro</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Auténtica receta yucateca marinada por 12 horas y cocida lentamente. Servida con cebolla morada y cilantro fresco.</t>
+          <t>Tacos tradicionales con tortillas hechas a mano, rellenas de cochinita pibil jugosa.</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/b12gUIRdrXZktUcZUoE2</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/XuN5cJ6SjLBPZvCtW8mZ</t>
         </is>
       </c>
       <c r="M17" s="1" t="n">
-        <v>46313.97784722222</v>
+        <v>46323.66122685185</v>
       </c>
     </row>
     <row r="18">
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>9.99</v>
+        <v>89</v>
       </c>
       <c r="G18" t="n">
         <v>580</v>
@@ -1450,11 +1450,11 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/hHNe0uQPUZ68qnkC6pEO</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/hHNe0uQPUZ68qnkC6pEO</t>
         </is>
       </c>
       <c r="M18" s="1" t="n">
-        <v>46313.97788194445</v>
+        <v>46323.66128472222</v>
       </c>
     </row>
     <row r="19">
@@ -1463,33 +1463,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dLFoAYOxzVWTMQ3xZ3JW</t>
+          <t>b12gUIRdrXZktUcZUoE2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sopas</t>
+          <t>Principales</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Consomé de Pollo</t>
+          <t>Cochinita Pibil Tradicional</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Consomé claro con pollo deshebrado, cebolla y cilantro</t>
+          <t>Carne de cerdo marinada en achiote, cocida lentamente en hojas de plátano</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4.49</v>
+        <v>149</v>
       </c>
       <c r="G19" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>300ml</t>
+          <t>200g</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1497,21 +1497,21 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Caldo claro, pollo deshebrado, cebolla, cilantro, limón</t>
+          <t>Cerdo, achiote, cítricos, hojas de plátano, especias yucatecas</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Consomé light y reconfortante, perfecto para acompañar cualquier platillo.</t>
+          <t>Auténtica receta yucateca marinada por 12 horas y cocida lentamente. Servida con cebolla morada y cilantro fresco.</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/dLFoAYOxzVWTMQ3xZ3JW</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/b12gUIRdrXZktUcZUoE2</t>
         </is>
       </c>
       <c r="M19" s="1" t="n">
-        <v>46313.97797453704</v>
+        <v>46323.66125</v>
       </c>
     </row>
     <row r="20">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>4.99</v>
+        <v>49</v>
       </c>
       <c r="G20" t="n">
         <v>280</v>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/SZNCnyrsRWzTqIMerWA7</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/SZNCnyrsRWzTqIMerWA7</t>
         </is>
       </c>
       <c r="M20" s="1" t="n">
-        <v>46313.97795138889</v>
+        <v>46323.66133101852</v>
       </c>
     </row>
     <row r="21">
@@ -1596,7 +1596,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4.99</v>
+        <v>49</v>
       </c>
       <c r="G21" t="n">
         <v>350</v>
@@ -1621,11 +1621,11 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/qzHJhzzRlZsaOdY5qb9U</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/qzHJhzzRlZsaOdY5qb9U</t>
         </is>
       </c>
       <c r="M21" s="1" t="n">
-        <v>46313.97800925926</v>
+        <v>46323.66138888889</v>
       </c>
     </row>
     <row r="22">
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5.49</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
         <v>320</v>
@@ -1678,11 +1678,68 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>http://localhost:3000/products/so2xk2zWk6eLNNp60ezt</t>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/so2xk2zWk6eLNNp60ezt</t>
         </is>
       </c>
       <c r="M22" s="1" t="n">
-        <v>46313.97803240741</v>
+        <v>46323.66142361111</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>dLFoAYOxzVWTMQ3xZ3JW</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sopas</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Consomé de Pollo</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Consomé claro con pollo deshebrado, cebolla y cilantro</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>59</v>
+      </c>
+      <c r="G23" t="n">
+        <v>200</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>300ml</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Caldo claro, pollo deshebrado, cebolla, cilantro, limón</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Consomé light y reconfortante, perfecto para acompañar cualquier platillo.</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://cochinita-pibil-pwa.vercel.app/products/dLFoAYOxzVWTMQ3xZ3JW</t>
+        </is>
+      </c>
+      <c r="M23" s="1" t="n">
+        <v>46323.66136574074</v>
       </c>
     </row>
   </sheetData>
@@ -1741,13 +1798,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>2.79</v>
+        <v>29.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1.99</v>
+        <v>21</v>
       </c>
       <c r="E2" t="n">
-        <v>3.49</v>
+        <v>35</v>
       </c>
       <c r="F2" t="n">
         <v>154</v>
@@ -1760,19 +1817,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>2.59</v>
+        <v>39.67</v>
       </c>
       <c r="D3" t="n">
-        <v>1.99</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>3.49</v>
+        <v>50</v>
       </c>
       <c r="F3" t="n">
-        <v>127.6</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="4">
@@ -1785,13 +1842,13 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7.99</v>
+        <v>77</v>
       </c>
       <c r="D4" t="n">
-        <v>5.99</v>
+        <v>35</v>
       </c>
       <c r="E4" t="n">
-        <v>9.99</v>
+        <v>149</v>
       </c>
       <c r="F4" t="n">
         <v>461.43</v>
@@ -1807,13 +1864,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.99</v>
+        <v>51.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4.49</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>5.49</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
         <v>287.5</v>
